--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.28667343782386</v>
+        <v>8.334084433646376</v>
       </c>
       <c r="D2" t="n">
-        <v>37.77122211750416</v>
+        <v>6.137823594094426</v>
       </c>
       <c r="E2" t="n">
-        <v>16.57005847492763</v>
+        <v>2.692634502175739</v>
       </c>
       <c r="F2" t="n">
-        <v>12.70811682103769</v>
+        <v>2.065068983418625</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.55480479109447</v>
+        <v>3.340155778552851</v>
       </c>
       <c r="D3" t="n">
-        <v>10.86630310684718</v>
+        <v>1.765774254862666</v>
       </c>
       <c r="E3" t="n">
-        <v>16.57005847492763</v>
+        <v>2.692634502175739</v>
       </c>
       <c r="F3" t="n">
-        <v>12.70811682103769</v>
+        <v>2.065068983418625</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12.95957717758253</v>
+        <v>2.105931291357161</v>
       </c>
       <c r="D4" t="n">
-        <v>10.76047920720045</v>
+        <v>1.748577871170073</v>
       </c>
       <c r="E4" t="n">
-        <v>16.57005847492763</v>
+        <v>2.692634502175739</v>
       </c>
       <c r="F4" t="n">
-        <v>12.70811682103769</v>
+        <v>2.065068983418625</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
